--- a/testcase_new/CI未运行测试用例.xlsx
+++ b/testcase_new/CI未运行测试用例.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7920"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7920" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="示例" sheetId="1" r:id="rId1"/>
+    <sheet name="测试用例" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>测试内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -81,12 +80,36 @@
     <t>特性名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>sdbreplay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/sdbreplay/sdbreplay_18598.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重放日志，数据跨多个日志文件（功能测试时此场景问题较多，该用例为保证此场景基本功能）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据量较大，且需要修改节点配置，并重启节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例已注释main函数，跑时请手工修改本地用例去注释</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -184,92 +207,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -304,7 +270,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -336,9 +302,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -370,6 +337,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -545,9 +513,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M126"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="7.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
@@ -559,7 +527,7 @@
     <col min="8" max="13" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -590,7 +558,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="40.5">
+    <row r="2" spans="1:13" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -619,7 +587,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -634,7 +602,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -649,7 +617,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -664,7 +632,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -679,7 +647,7 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -694,7 +662,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13" s="6" customFormat="1">
+    <row r="8" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -709,7 +677,7 @@
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -724,7 +692,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -737,7 +705,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -752,7 +720,7 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -767,7 +735,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -782,7 +750,7 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -797,7 +765,7 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -812,7 +780,7 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -827,7 +795,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -842,7 +810,7 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -857,7 +825,7 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -872,7 +840,7 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -887,7 +855,7 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -902,7 +870,7 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -917,7 +885,7 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -932,7 +900,7 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -947,7 +915,7 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -962,7 +930,7 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -977,7 +945,7 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -992,7 +960,7 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1007,7 +975,7 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1022,7 +990,7 @@
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1037,7 +1005,7 @@
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1052,7 +1020,7 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1063,7 +1031,7 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1074,7 +1042,7 @@
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1085,7 +1053,7 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1096,7 +1064,7 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1107,7 +1075,7 @@
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1118,7 +1086,7 @@
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1129,7 +1097,7 @@
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1140,7 +1108,7 @@
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1151,7 +1119,7 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1162,7 +1130,7 @@
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1173,7 +1141,7 @@
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1184,7 +1152,7 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1195,7 +1163,7 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1206,7 +1174,7 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1217,7 +1185,7 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1228,7 +1196,7 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1239,7 +1207,7 @@
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1250,7 +1218,7 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1261,7 +1229,7 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1272,7 +1240,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1283,7 +1251,7 @@
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1294,7 +1262,7 @@
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1305,7 +1273,7 @@
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1316,7 +1284,7 @@
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1327,7 +1295,7 @@
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1338,7 +1306,7 @@
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1349,7 +1317,7 @@
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -1360,7 +1328,7 @@
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -1371,7 +1339,7 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="1:9" ht="27">
+    <row r="61" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>2</v>
       </c>
@@ -1383,7 +1351,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -1394,7 +1362,7 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -1404,7 +1372,7 @@
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -1415,7 +1383,7 @@
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1426,7 +1394,7 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1437,7 +1405,7 @@
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1448,7 +1416,7 @@
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -1459,7 +1427,7 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="1:9" ht="40.5">
+    <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>1</v>
       </c>
@@ -1471,7 +1439,7 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -1482,7 +1450,7 @@
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -1493,7 +1461,7 @@
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -1504,7 +1472,7 @@
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -1515,7 +1483,7 @@
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -1526,7 +1494,7 @@
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -1537,7 +1505,7 @@
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -1548,7 +1516,7 @@
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -1559,7 +1527,7 @@
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -1570,7 +1538,7 @@
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -1581,7 +1549,7 @@
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -1592,7 +1560,7 @@
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -1603,7 +1571,7 @@
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -1614,7 +1582,7 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -1625,7 +1593,7 @@
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -1636,7 +1604,7 @@
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -1647,7 +1615,7 @@
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -1658,7 +1626,7 @@
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -1669,7 +1637,7 @@
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -1680,7 +1648,7 @@
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -1691,7 +1659,7 @@
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -1702,7 +1670,7 @@
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -1713,7 +1681,7 @@
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -1724,7 +1692,7 @@
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -1735,7 +1703,7 @@
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -1746,7 +1714,7 @@
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -1757,7 +1725,7 @@
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -1768,7 +1736,7 @@
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -1779,7 +1747,7 @@
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -1790,7 +1758,7 @@
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -1801,7 +1769,7 @@
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -1812,7 +1780,7 @@
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -1823,7 +1791,7 @@
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -1834,7 +1802,7 @@
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -1845,7 +1813,7 @@
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -1856,7 +1824,7 @@
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -1867,7 +1835,7 @@
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -1878,7 +1846,7 @@
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -1889,7 +1857,7 @@
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -1900,7 +1868,7 @@
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -1911,7 +1879,7 @@
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -1922,7 +1890,7 @@
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -1933,7 +1901,7 @@
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -1944,7 +1912,7 @@
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -1955,7 +1923,7 @@
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -1966,7 +1934,7 @@
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -1977,7 +1945,7 @@
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -1988,7 +1956,7 @@
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -1999,7 +1967,7 @@
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -2010,7 +1978,7 @@
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -2021,7 +1989,7 @@
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -2032,7 +2000,7 @@
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -2043,7 +2011,7 @@
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -2054,7 +2022,7 @@
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -2065,7 +2033,7 @@
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -2076,7 +2044,7 @@
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -2087,7 +2055,7 @@
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -2106,21 +2074,1565 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M126"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="7.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="35" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="8">
+        <v>43655</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" s="7"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="A69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="7"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/testcase_new/CI未运行测试用例.xlsx
+++ b/testcase_new/CI未运行测试用例.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>测试内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -102,6 +102,14 @@
   </si>
   <si>
     <t>用例已注释main函数，跑时请手工修改本地用例去注释</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>story</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2075,83 +2083,89 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="7.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="35" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="9" style="2"/>
+    <col min="1" max="2" width="7.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" ht="27" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="8">
+      <c r="I2" s="8">
         <v>43655</v>
       </c>
-      <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2165,8 +2179,9 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2180,8 +2195,9 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -2195,8 +2211,9 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -2210,8 +2227,9 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -2225,12 +2243,13 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -2240,8 +2259,9 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N8" s="5"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2255,21 +2275,23 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="E10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2283,8 +2305,9 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2298,8 +2321,9 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -2313,8 +2337,9 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2328,23 +2353,25 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="3"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2358,8 +2385,9 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2373,8 +2401,9 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2388,8 +2417,9 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2403,8 +2433,9 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2418,8 +2449,9 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2433,8 +2465,9 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2448,8 +2481,9 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2463,8 +2497,9 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2478,8 +2513,9 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2493,8 +2529,9 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2508,8 +2545,9 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2523,8 +2561,9 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2538,8 +2577,9 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2553,8 +2593,9 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2568,8 +2609,9 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2583,8 +2625,9 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2594,8 +2637,9 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2605,8 +2649,9 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2616,8 +2661,9 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2627,8 +2673,9 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2638,8 +2685,9 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2649,8 +2697,9 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2660,8 +2709,9 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2671,8 +2721,9 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2682,8 +2733,9 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2693,8 +2745,9 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2704,8 +2757,9 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2715,8 +2769,9 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2726,8 +2781,9 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2737,8 +2793,9 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2748,8 +2805,9 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2759,8 +2817,9 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2770,8 +2829,9 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2781,8 +2841,9 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2792,8 +2853,9 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2803,8 +2865,9 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2814,8 +2877,9 @@
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2825,8 +2889,9 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2836,8 +2901,9 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2847,8 +2913,9 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2858,8 +2925,9 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2869,8 +2937,9 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2880,8 +2949,9 @@
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2891,8 +2961,9 @@
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2902,20 +2973,22 @@
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="D61" s="1"/>
+      <c r="C61" s="7"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2925,18 +2998,20 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
-      <c r="E63" s="1"/>
+      <c r="D63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2946,8 +3021,9 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2957,8 +3033,9 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2968,8 +3045,9 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2979,8 +3057,9 @@
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J67" s="1"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2990,20 +3069,22 @@
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+      <c r="J68" s="1"/>
+    </row>
+    <row r="69" spans="1:10" ht="81" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B69" s="7"/>
-      <c r="D69" s="1"/>
+      <c r="C69" s="7"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J69" s="1"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3013,8 +3094,9 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3024,8 +3106,9 @@
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3035,8 +3118,9 @@
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J72" s="1"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3046,8 +3130,9 @@
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3057,8 +3142,9 @@
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3068,8 +3154,9 @@
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3079,8 +3166,9 @@
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3090,8 +3178,9 @@
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3101,8 +3190,9 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3112,8 +3202,9 @@
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3123,8 +3214,9 @@
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3134,8 +3226,9 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3145,8 +3238,9 @@
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J82" s="1"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3156,8 +3250,9 @@
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J83" s="1"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3167,8 +3262,9 @@
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3178,8 +3274,9 @@
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3189,8 +3286,9 @@
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3200,8 +3298,9 @@
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3211,8 +3310,9 @@
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3222,8 +3322,9 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3233,8 +3334,9 @@
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3244,8 +3346,9 @@
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3255,8 +3358,9 @@
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3266,8 +3370,9 @@
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J93" s="1"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3277,8 +3382,9 @@
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3288,8 +3394,9 @@
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3299,8 +3406,9 @@
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3310,8 +3418,9 @@
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3321,8 +3430,9 @@
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J98" s="1"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3332,8 +3442,9 @@
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J99" s="1"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3343,8 +3454,9 @@
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J100" s="1"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3354,8 +3466,9 @@
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J101" s="1"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3365,8 +3478,9 @@
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J102" s="1"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3376,8 +3490,9 @@
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J103" s="1"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3387,8 +3502,9 @@
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J104" s="1"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3398,8 +3514,9 @@
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J105" s="1"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3409,8 +3526,9 @@
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J106" s="1"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3420,8 +3538,9 @@
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J107" s="1"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3431,8 +3550,9 @@
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J108" s="1"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3442,8 +3562,9 @@
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J109" s="1"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3453,8 +3574,9 @@
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J110" s="1"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3464,8 +3586,9 @@
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J111" s="1"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3475,8 +3598,9 @@
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J112" s="1"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3486,8 +3610,9 @@
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J113" s="1"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3497,8 +3622,9 @@
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J114" s="1"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3508,8 +3634,9 @@
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J115" s="1"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3519,8 +3646,9 @@
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J116" s="1"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3530,8 +3658,9 @@
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3541,8 +3670,9 @@
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3552,8 +3682,9 @@
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J119" s="1"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3563,8 +3694,9 @@
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3574,8 +3706,9 @@
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J121" s="1"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3585,8 +3718,9 @@
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3596,8 +3730,9 @@
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J123" s="1"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3607,8 +3742,9 @@
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J124" s="1"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3618,8 +3754,9 @@
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3629,6 +3766,7 @@
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
